--- a/gallabox_scenarios.xlsx
+++ b/gallabox_scenarios.xlsx
@@ -449,7 +449,19 @@
         <v>POST https://api.metrogini.com/api/whatsapp/session</v>
       </c>
       <c r="D2" t="str" xml:space="preserve">
-        <v xml:space="preserve">{
+        <v xml:space="preserve">========== FIELD GUIDE ==========
+REQUIRED: mobile
+OPTIONAL: none
+=================================
+How to use in Postman:
+- OPTIONAL query params are unchecked (disabled). Tick only if needed.
+- Body tab sends clean JSON (no comments).
+- Annotated body below is documentation for Gallabox (which fields are optional).
+Annotated body (docs only — do not paste comments into Body):
+{
+  "mobile": "{{mobile}}"  // REQUIRED
+}
+{
   "mobile": "9004186460"
 }
 Required: mobile
@@ -491,7 +503,19 @@
         <v>POST https://api.metrogini.com/api/whatsapp/customer/lookup</v>
       </c>
       <c r="D3" t="str" xml:space="preserve">
-        <v xml:space="preserve">{
+        <v xml:space="preserve">========== FIELD GUIDE ==========
+REQUIRED: mobile
+OPTIONAL: none
+=================================
+How to use in Postman:
+- OPTIONAL query params are unchecked (disabled). Tick only if needed.
+- Body tab sends clean JSON (no comments).
+- Annotated body below is documentation for Gallabox (which fields are optional).
+Annotated body (docs only — do not paste comments into Body):
+{
+  "mobile": "{{mobile}}"  // REQUIRED
+}
+{
   "mobile": "9004186460"
 }
 Required: mobile
@@ -534,7 +558,19 @@
         <v>POST https://api.metrogini.com/api/user/login-or-register</v>
       </c>
       <c r="D4" t="str" xml:space="preserve">
-        <v xml:space="preserve">{
+        <v xml:space="preserve">========== FIELD GUIDE ==========
+REQUIRED: mobile
+OPTIONAL: none
+=================================
+How to use in Postman:
+- OPTIONAL query params are unchecked (disabled). Tick only if needed.
+- Body tab sends clean JSON (no comments).
+- Annotated body below is documentation for Gallabox (which fields are optional).
+Annotated body (docs only — do not paste comments into Body):
+{
+  "mobile": "{{mobile}}"  // REQUIRED
+}
+{
   "mobile": "9004186460"
 }
 Required: mobile
@@ -565,7 +601,20 @@
         <v>POST https://api.metrogini.com/api/user/verify-otp</v>
       </c>
       <c r="D5" t="str" xml:space="preserve">
-        <v xml:space="preserve">{
+        <v xml:space="preserve">========== FIELD GUIDE ==========
+REQUIRED: mobile, otp
+OPTIONAL: none
+=================================
+How to use in Postman:
+- OPTIONAL query params are unchecked (disabled). Tick only if needed.
+- Body tab sends clean JSON (no comments).
+- Annotated body below is documentation for Gallabox (which fields are optional).
+Annotated body (docs only — do not paste comments into Body):
+{
+  "mobile": "{{mobile}}",  // REQUIRED
+  "otp": "1234"  // REQUIRED
+}
+{
   "mobile": "9004186460",
   "otp": "1234"
 }
@@ -597,7 +646,21 @@
         <v>POST https://api.metrogini.com/api/whatsapp/events/emit</v>
       </c>
       <c r="D6" t="str" xml:space="preserve">
-        <v xml:space="preserve">{
+        <v xml:space="preserve">========== FIELD GUIDE ==========
+REQUIRED: event
+OPTIONAL: order_id, mobile, data
+=================================
+How to use in Postman:
+- OPTIONAL query params are unchecked (disabled). Tick only if needed.
+- Body tab sends clean JSON (no comments).
+- Annotated body below is documentation for Gallabox (which fields are optional).
+Annotated body (docs only — do not paste comments into Body):
+{
+  "event": "pickup_day_reminder",  // REQUIRED
+  "order_id": "{{orderId}}",  // OPTIONAL — can omit
+  "data": {}  // OPTIONAL — can omit
+}
+{
   "event": "pickup_day_reminder",
   "order_id": 74,
   "mobile": "9004186460",
@@ -667,7 +730,19 @@
         <v>POST https://api.metrogini.com/api/whatsapp/customer/lookup</v>
       </c>
       <c r="D2" t="str" xml:space="preserve">
-        <v xml:space="preserve">{
+        <v xml:space="preserve">========== FIELD GUIDE ==========
+REQUIRED: mobile
+OPTIONAL: none
+=================================
+How to use in Postman:
+- OPTIONAL query params are unchecked (disabled). Tick only if needed.
+- Body tab sends clean JSON (no comments).
+- Annotated body below is documentation for Gallabox (which fields are optional).
+Annotated body (docs only — do not paste comments into Body):
+{
+  "mobile": "{{mobile}}"  // REQUIRED
+}
+{
   "mobile": "9004186460"
 }
 Required: mobile
@@ -697,7 +772,19 @@
         <v>POST https://api.metrogini.com/api/whatsapp/session</v>
       </c>
       <c r="D3" t="str" xml:space="preserve">
-        <v xml:space="preserve">{
+        <v xml:space="preserve">========== FIELD GUIDE ==========
+REQUIRED: mobile
+OPTIONAL: none
+=================================
+How to use in Postman:
+- OPTIONAL query params are unchecked (disabled). Tick only if needed.
+- Body tab sends clean JSON (no comments).
+- Annotated body below is documentation for Gallabox (which fields are optional).
+Annotated body (docs only — do not paste comments into Body):
+{
+  "mobile": "{{mobile}}"  // REQUIRED
+}
+{
   "mobile": "9004186460"
 }
 Required: mobile
@@ -777,7 +864,19 @@
         <v>POST https://api.metrogini.com/api/whatsapp/customer/lookup</v>
       </c>
       <c r="D2" t="str" xml:space="preserve">
-        <v xml:space="preserve">{
+        <v xml:space="preserve">========== FIELD GUIDE ==========
+REQUIRED: mobile
+OPTIONAL: none
+=================================
+How to use in Postman:
+- OPTIONAL query params are unchecked (disabled). Tick only if needed.
+- Body tab sends clean JSON (no comments).
+- Annotated body below is documentation for Gallabox (which fields are optional).
+Annotated body (docs only — do not paste comments into Body):
+{
+  "mobile": "{{mobile}}"  // REQUIRED
+}
+{
   "mobile": "9004186460"
 }
 Required: mobile
@@ -819,7 +918,19 @@
         <v>POST https://api.metrogini.com/api/whatsapp/session</v>
       </c>
       <c r="D3" t="str" xml:space="preserve">
-        <v xml:space="preserve">{
+        <v xml:space="preserve">========== FIELD GUIDE ==========
+REQUIRED: mobile
+OPTIONAL: none
+=================================
+How to use in Postman:
+- OPTIONAL query params are unchecked (disabled). Tick only if needed.
+- Body tab sends clean JSON (no comments).
+- Annotated body below is documentation for Gallabox (which fields are optional).
+Annotated body (docs only — do not paste comments into Body):
+{
+  "mobile": "{{mobile}}"  // REQUIRED
+}
+{
   "mobile": "9004186460"
 }
 Required: mobile
@@ -860,7 +971,19 @@
         <v>GET https://api.metrogini.com/api/user/order/getUserOrder</v>
       </c>
       <c r="D4" t="str" xml:space="preserve">
-        <v xml:space="preserve">Query optional: status, time, page, limit
+        <v xml:space="preserve">========== FIELD GUIDE ==========
+REQUIRED: none (no body)
+OPTIONAL: status, time, page, limit
+=================================
+How to use in Postman:
+- OPTIONAL query params are unchecked (disabled). Tick only if needed.
+- Body tab sends clean JSON (no comments).
+- Annotated body below is documentation for Gallabox (which fields are optional).
+Query params:
+  • status: OPTIONAL — Optional filter
+  • page: OPTIONAL — Optional
+  • limit: OPTIONAL — Optional
+Query optional: status, time, page, limit
 status: booked | out_for_pickup | pickup_in_progress | picked_up | in_process | order_finalized | ready_for_delivery | out_for_delivery | delivered | cancelled</v>
       </c>
       <c r="E4" t="str" xml:space="preserve">
@@ -889,7 +1012,15 @@
         <v>GET https://api.metrogini.com/api/user/order/:id/Orderdetail</v>
       </c>
       <c r="D5" t="str" xml:space="preserve">
-        <v xml:space="preserve">Path required: id
+        <v xml:space="preserve">========== FIELD GUIDE ==========
+REQUIRED: id
+OPTIONAL: none
+=================================
+How to use in Postman:
+- OPTIONAL query params are unchecked (disabled). Tick only if needed.
+- Body tab sends clean JSON (no comments).
+- Annotated body below is documentation for Gallabox (which fields are optional).
+Path required: id
 Optional: none</v>
       </c>
       <c r="E5" t="str" xml:space="preserve">
@@ -916,7 +1047,17 @@
         <v>GET https://api.metrogini.com/api/whatsapp/orders/active-by-mobile</v>
       </c>
       <c r="D6" t="str" xml:space="preserve">
-        <v xml:space="preserve">Query required: mobile
+        <v xml:space="preserve">========== FIELD GUIDE ==========
+REQUIRED: mobile
+OPTIONAL: none
+=================================
+How to use in Postman:
+- OPTIONAL query params are unchecked (disabled). Tick only if needed.
+- Body tab sends clean JSON (no comments).
+- Annotated body below is documentation for Gallabox (which fields are optional).
+Query params:
+  • mobile: REQUIRED (or usually sent) — Required
+Query required: mobile
 Optional: none</v>
       </c>
       <c r="E6" t="str" xml:space="preserve">
@@ -983,7 +1124,19 @@
         <v>POST https://api.metrogini.com/api/whatsapp/session</v>
       </c>
       <c r="D2" t="str" xml:space="preserve">
-        <v xml:space="preserve">{
+        <v xml:space="preserve">========== FIELD GUIDE ==========
+REQUIRED: mobile
+OPTIONAL: none
+=================================
+How to use in Postman:
+- OPTIONAL query params are unchecked (disabled). Tick only if needed.
+- Body tab sends clean JSON (no comments).
+- Annotated body below is documentation for Gallabox (which fields are optional).
+Annotated body (docs only — do not paste comments into Body):
+{
+  "mobile": "{{mobile}}"  // REQUIRED
+}
+{
   "mobile": "9004186460"
 }
 Required: mobile
@@ -1024,7 +1177,17 @@
         <v>GET https://api.metrogini.com/api/whatsapp/orders/active-by-mobile</v>
       </c>
       <c r="D3" t="str" xml:space="preserve">
-        <v xml:space="preserve">Query required: mobile
+        <v xml:space="preserve">========== FIELD GUIDE ==========
+REQUIRED: mobile
+OPTIONAL: none
+=================================
+How to use in Postman:
+- OPTIONAL query params are unchecked (disabled). Tick only if needed.
+- Body tab sends clean JSON (no comments).
+- Annotated body below is documentation for Gallabox (which fields are optional).
+Query params:
+  • mobile: REQUIRED (or usually sent) — Required
+Query required: mobile
 Optional: none</v>
       </c>
       <c r="E3" t="str" xml:space="preserve">
@@ -1051,7 +1214,15 @@
         <v>GET https://api.metrogini.com/api/user/order/:id/Orderdetail</v>
       </c>
       <c r="D4" t="str" xml:space="preserve">
-        <v xml:space="preserve">Path required: id
+        <v xml:space="preserve">========== FIELD GUIDE ==========
+REQUIRED: id
+OPTIONAL: none
+=================================
+How to use in Postman:
+- OPTIONAL query params are unchecked (disabled). Tick only if needed.
+- Body tab sends clean JSON (no comments).
+- Annotated body below is documentation for Gallabox (which fields are optional).
+Path required: id
 Optional: none</v>
       </c>
       <c r="E4" t="str" xml:space="preserve">
@@ -1078,7 +1249,15 @@
         <v>GET https://api.metrogini.com/api/whatsapp/orders/:id/delay-status</v>
       </c>
       <c r="D5" t="str" xml:space="preserve">
-        <v xml:space="preserve">Path required: id
+        <v xml:space="preserve">========== FIELD GUIDE ==========
+REQUIRED: id
+OPTIONAL: none
+=================================
+How to use in Postman:
+- OPTIONAL query params are unchecked (disabled). Tick only if needed.
+- Body tab sends clean JSON (no comments).
+- Annotated body below is documentation for Gallabox (which fields are optional).
+Path required: id
 Optional: none</v>
       </c>
       <c r="E5" t="str" xml:space="preserve">
@@ -1106,7 +1285,21 @@
         <v>POST https://api.metrogini.com/api/user/needHelp</v>
       </c>
       <c r="D6" t="str" xml:space="preserve">
-        <v xml:space="preserve">{
+        <v xml:space="preserve">========== FIELD GUIDE ==========
+REQUIRED: message
+OPTIONAL: report_issue. Required: message
+=================================
+How to use in Postman:
+- OPTIONAL query params are unchecked (disabled). Tick only if needed.
+- Body tab sends clean JSON (no comments).
+- Annotated body below is documentation for Gallabox (which fields are optional).
+Annotated body (docs only — do not paste comments into Body):
+{
+  "report_issue": "delay",  // OPTIONAL — can omit
+  "message": "Pickup delayed"  // REQUIRED
+}
+OPTIONAL: report_issue. Required: message
+{
   "report_issue": "delay",
   "message": "Pickup delayed"
 }
@@ -1173,7 +1366,19 @@
         <v>POST https://api.metrogini.com/api/whatsapp/session</v>
       </c>
       <c r="D2" t="str" xml:space="preserve">
-        <v xml:space="preserve">{
+        <v xml:space="preserve">========== FIELD GUIDE ==========
+REQUIRED: mobile
+OPTIONAL: none
+=================================
+How to use in Postman:
+- OPTIONAL query params are unchecked (disabled). Tick only if needed.
+- Body tab sends clean JSON (no comments).
+- Annotated body below is documentation for Gallabox (which fields are optional).
+Annotated body (docs only — do not paste comments into Body):
+{
+  "mobile": "{{mobile}}"  // REQUIRED
+}
+{
   "mobile": "9004186460"
 }
 Required: mobile
@@ -1214,7 +1419,17 @@
         <v>GET https://api.metrogini.com/api/common/pincode-check</v>
       </c>
       <c r="D3" t="str" xml:space="preserve">
-        <v xml:space="preserve">Query required: pincode
+        <v xml:space="preserve">========== FIELD GUIDE ==========
+REQUIRED: pincode
+OPTIONAL: none
+=================================
+How to use in Postman:
+- OPTIONAL query params are unchecked (disabled). Tick only if needed.
+- Body tab sends clean JSON (no comments).
+- Annotated body below is documentation for Gallabox (which fields are optional).
+Query params:
+  • pincode: REQUIRED (or usually sent) — Required. 6-digit pincode
+Query required: pincode
 Optional: none
 If serviceable=false → coming soon; stop.</v>
       </c>
@@ -1248,7 +1463,19 @@
         <v>GET https://api.metrogini.com/api/common/pincodes</v>
       </c>
       <c r="D4" t="str" xml:space="preserve">
-        <v xml:space="preserve">Query optional: pincode, pincode_group_id, serviceable (true/false)
+        <v xml:space="preserve">========== FIELD GUIDE ==========
+REQUIRED: none (no body)
+OPTIONAL: pincode, pincode_group_id, serviceable (true/false)
+=================================
+How to use in Postman:
+- OPTIONAL query params are unchecked (disabled). Tick only if needed.
+- Body tab sends clean JSON (no comments).
+- Annotated body below is documentation for Gallabox (which fields are optional).
+Query params:
+  • pincode: OPTIONAL — Optional. Exact pincode
+  • pincode_group_id: OPTIONAL — Optional
+  • serviceable: OPTIONAL — Optional: true | false
+Query optional: pincode, pincode_group_id, serviceable (true/false)
 Prefer pincode-check for WhatsApp.</v>
       </c>
       <c r="E4" t="str" xml:space="preserve">
@@ -1277,7 +1504,18 @@
         <v>GET https://api.metrogini.com/api/common/services</v>
       </c>
       <c r="D5" t="str" xml:space="preserve">
-        <v xml:space="preserve">Query optional: pincode OR pincode_group_id (or zone_id)
+        <v xml:space="preserve">========== FIELD GUIDE ==========
+REQUIRED: none (no body)
+OPTIONAL: pincode OR pincode_group_id (or zone_id)
+=================================
+How to use in Postman:
+- OPTIONAL query params are unchecked (disabled). Tick only if needed.
+- Body tab sends clean JSON (no comments).
+- Annotated body below is documentation for Gallabox (which fields are optional).
+Query params:
+  • pincode: REQUIRED (or usually sent) — Optional
+  • pincode_group_id: OPTIONAL — Optional
+Query optional: pincode OR pincode_group_id (or zone_id)
 If omitted, default service prices.</v>
       </c>
       <c r="E5" t="str" xml:space="preserve">
@@ -1308,8 +1546,16 @@
       <c r="C6" t="str">
         <v>GET https://api.metrogini.com/api/common/service-types</v>
       </c>
-      <c r="D6" t="str">
-        <v>No body. Optional: none</v>
+      <c r="D6" t="str" xml:space="preserve">
+        <v xml:space="preserve">========== FIELD GUIDE ==========
+REQUIRED: none (no body)
+OPTIONAL: none
+=================================
+How to use in Postman:
+- OPTIONAL query params are unchecked (disabled). Tick only if needed.
+- Body tab sends clean JSON (no comments).
+- Annotated body below is documentation for Gallabox (which fields are optional).
+No body. Optional: none</v>
       </c>
       <c r="E6" t="str" xml:space="preserve">
         <v xml:space="preserve">{
@@ -1332,39 +1578,59 @@
         <v>Scenario 1 — Promotion / New Customer(Send)</v>
       </c>
       <c r="B7" t="str">
-        <v>Add address</v>
+        <v>Add address (Gallabox simple)</v>
       </c>
       <c r="C7" t="str">
-        <v>POST https://api.metrogini.com/api/user/address</v>
+        <v>POST https://api.metrogini.com/api/whatsapp/address</v>
       </c>
       <c r="D7" t="str" xml:space="preserve">
-        <v xml:space="preserve">{
-  "address_type": "home",
-  "floor": "204",
-  "landmark": "Near station",
-  "receiver_name": "Karthik",
-  "contact_number": "9004186460",
-  "latitude": "19.1197",
-  "longitude": "72.8468",
+        <v xml:space="preserve">========== FIELD GUIDE ==========
+REQUIRED: mobile, complete_address, pincode, name, email
+OPTIONAL: none
+=================================
+How to use in Postman:
+- OPTIONAL query params are unchecked (disabled). Tick only if needed.
+- Body tab sends clean JSON (no comments).
+- Annotated body below is documentation for Gallabox (which fields are optional).
+Annotated body (docs only — do not paste comments into Body):
+{
+  "mobile": "{{mobile}}",  // REQUIRED
+  "complete_address": "A-204, Lotus Residency, Andheri West",  // REQUIRED
+  "pincode": "{{pincode}}",  // REQUIRED
+  "name": "Karthik",  // REQUIRED
+  "email": "karthik@example.com"  // REQUIRED
+}
+Gallabox: mobile + complete_address + pincode + name + email (all required). No separate set-default call.
+{
+  "mobile": "9004186460",
+  "complete_address": "A-204, Lotus Residency, Andheri West",
   "pincode": "400058",
-  "complete_address": "A-204, Lotus Residency, Andheri West",
   "name": "Karthik",
   "email": "karthik@example.com"
 }
-Required: address_type (home|work|institute), floor, landmark, receiver_name (or name), contact_number, latitude, longitude, pincode
-Optional: complete_address, name, email</v>
+Required: mobile, complete_address, pincode, name, email
+Optional: none
+Server splits floor/landmark from complete_address and auto-sets default. Returns access_token for booking steps.</v>
       </c>
       <c r="E7" t="str" xml:space="preserve">
         <v xml:space="preserve">{
   "success": true,
-  "message": "Address added successfully",
+  "message": "Address added and set as default",
   "data": {
-    "address_id": 3
+    "address_id": 3,
+    "is_default": true,
+    "pincode": "400058",
+    "complete_address": "A-204, Lotus Residency, Andheri West",
+    "floor": "A-204",
+    "landmark": "Lotus Residency",
+    "name": "Karthik",
+    "email": "karthik@example.com",
+    "access_token": "eyJ..."
   }
 }</v>
       </c>
       <c r="F7" t="str">
-        <v>Yes (user Bearer)</v>
+        <v>Gallabox secret</v>
       </c>
     </row>
     <row r="8" xml:space="preserve">
@@ -1372,15 +1638,24 @@
         <v>Scenario 1 — Promotion / New Customer(Send)</v>
       </c>
       <c r="B8" t="str">
-        <v>Set default address</v>
+        <v>Set default address (app only — skip on WhatsApp)</v>
       </c>
       <c r="C8" t="str">
         <v>PUT https://api.metrogini.com/api/user/address/default/:id</v>
       </c>
       <c r="D8" t="str" xml:space="preserve">
-        <v xml:space="preserve">No body.
+        <v xml:space="preserve">========== FIELD GUIDE ==========
+REQUIRED: id = address_id
+OPTIONAL: none
+=================================
+How to use in Postman:
+- OPTIONAL query params are unchecked (disabled). Tick only if needed.
+- Body tab sends clean JSON (no comments).
+- Annotated body below is documentation for Gallabox (which fields are optional).
+No body.
 Path required: id = address_id
-Optional: none</v>
+Optional: none
+WhatsApp: skip — POST /api/whatsapp/address already sets default.</v>
       </c>
       <c r="E8" t="str" xml:space="preserve">
         <v xml:space="preserve">{
@@ -1403,7 +1678,19 @@
         <v>GET https://api.metrogini.com/api/common/slots/availability</v>
       </c>
       <c r="D9" t="str" xml:space="preserve">
-        <v xml:space="preserve">Required: pincode OR pincodeGroupId (or pincode_group_id)
+        <v xml:space="preserve">========== FIELD GUIDE ==========
+REQUIRED: pincode OR pincodeGroupId (or pincode_group_id)
+OPTIONAL: days (default 7)
+=================================
+How to use in Postman:
+- OPTIONAL query params are unchecked (disabled). Tick only if needed.
+- Body tab sends clean JSON (no comments).
+- Annotated body below is documentation for Gallabox (which fields are optional).
+Query params:
+  • pincode: REQUIRED (or usually sent) — Required unless pincodeGroupId
+  • pincodeGroupId: OPTIONAL — Optional (use instead of pincode)
+  • days: OPTIONAL — Optional. Default 7
+Required: pincode OR pincodeGroupId (or pincode_group_id)
 Optional: days (default 7)</v>
       </c>
       <c r="E9" t="str" xml:space="preserve">
@@ -1441,7 +1728,20 @@
         <v>POST https://api.metrogini.com/api/user/order/</v>
       </c>
       <c r="D10" t="str" xml:space="preserve">
-        <v xml:space="preserve">{
+        <v xml:space="preserve">========== FIELD GUIDE ==========
+REQUIRED: service_id, clothes_count (10–25)
+OPTIONAL: none
+=================================
+How to use in Postman:
+- OPTIONAL query params are unchecked (disabled). Tick only if needed.
+- Body tab sends clean JSON (no comments).
+- Annotated body below is documentation for Gallabox (which fields are optional).
+Annotated body (docs only — do not paste comments into Body):
+{
+  "service_id": 1,  // REQUIRED
+  "clothes_count": 15  // REQUIRED
+}
+{
   "service_id": 1,
   "clothes_count": 15
 }
@@ -1470,7 +1770,22 @@
         <v>POST https://api.metrogini.com/api/user/order/:id/complete-order</v>
       </c>
       <c r="D11" t="str" xml:space="preserve">
-        <v xml:space="preserve">{
+        <v xml:space="preserve">========== FIELD GUIDE ==========
+REQUIRED: service_type_id, pickup_date, pickup_slot_id, next_delivery_date
+OPTIONAL: none
+=================================
+How to use in Postman:
+- OPTIONAL query params are unchecked (disabled). Tick only if needed.
+- Body tab sends clean JSON (no comments).
+- Annotated body below is documentation for Gallabox (which fields are optional).
+Annotated body (docs only — do not paste comments into Body):
+{
+  "service_type_id": 1,  // REQUIRED
+  "pickup_date": "2026-09-10",  // REQUIRED
+  "pickup_slot_id": 1,  // REQUIRED
+  "next_delivery_date": "2026-09-13"  // REQUIRED
+}
+{
   "service_type_id": 1,
   "pickup_date": "2026-09-10",
   "pickup_slot_id": 1,
@@ -1502,7 +1817,15 @@
         <v>GET https://api.metrogini.com/api/user/order/:id/review</v>
       </c>
       <c r="D12" t="str" xml:space="preserve">
-        <v xml:space="preserve">No body. Path required: id
+        <v xml:space="preserve">========== FIELD GUIDE ==========
+REQUIRED: id
+OPTIONAL: none. Loyalty coupon auto-applies.
+=================================
+How to use in Postman:
+- OPTIONAL query params are unchecked (disabled). Tick only if needed.
+- Body tab sends clean JSON (no comments).
+- Annotated body below is documentation for Gallabox (which fields are optional).
+No body. Path required: id
 Optional: none. Loyalty coupon auto-applies.</v>
       </c>
       <c r="E12" t="str" xml:space="preserve">
@@ -1530,7 +1853,21 @@
         <v>POST https://api.metrogini.com/api/user/order/payment/:id/pay</v>
       </c>
       <c r="D13" t="str" xml:space="preserve">
-        <v xml:space="preserve">{
+        <v xml:space="preserve">========== FIELD GUIDE ==========
+REQUIRED: group_code, shift_id, day_of_week (1=Mon…7=Sun)
+OPTIONAL: none
+=================================
+How to use in Postman:
+- OPTIONAL query params are unchecked (disabled). Tick only if needed.
+- Body tab sends clean JSON (no comments).
+- Annotated body below is documentation for Gallabox (which fields are optional).
+Annotated body (docs only — do not paste comments into Body):
+{
+  "group_code": "{{groupCode}}",  // REQUIRED
+  "shift_id": 1,  // REQUIRED
+  "day_of_week": 3  // REQUIRED
+}
+{
   "group_code": "MUM_WEST",
   "shift_id": 1,
   "day_of_week": 3
@@ -1562,7 +1899,15 @@
         <v>GET https://api.metrogini.com/api/user/order/:id/Orderdetail</v>
       </c>
       <c r="D14" t="str" xml:space="preserve">
-        <v xml:space="preserve">No body. Path required: id
+        <v xml:space="preserve">========== FIELD GUIDE ==========
+REQUIRED: id
+OPTIONAL: none
+=================================
+How to use in Postman:
+- OPTIONAL query params are unchecked (disabled). Tick only if needed.
+- Body tab sends clean JSON (no comments).
+- Annotated body below is documentation for Gallabox (which fields are optional).
+No body. Path required: id
 Optional: none</v>
       </c>
       <c r="E14" t="str" xml:space="preserve">
@@ -1590,7 +1935,21 @@
         <v>POST https://api.metrogini.com/api/user/order/:id/cancelService</v>
       </c>
       <c r="D15" t="str" xml:space="preserve">
-        <v xml:space="preserve">{
+        <v xml:space="preserve">========== FIELD GUIDE ==========
+REQUIRED: reason_type (pickup_schedule_issue | modify_order | service_charge_incorrect | changed_mind | other)
+OPTIONAL: reason_description (required only when reason_type = other)
+=================================
+How to use in Postman:
+- OPTIONAL query params are unchecked (disabled). Tick only if needed.
+- Body tab sends clean JSON (no comments).
+- Annotated body below is documentation for Gallabox (which fields are optional).
+Annotated body (docs only — do not paste comments into Body):
+{
+  "reason_type": "changed_mind",  // REQUIRED
+  "reason_description": "Customer pressed C on WhatsApp"  // OPTIONAL — can omit
+}
+OPTIONAL: reason_description (required only when reason_type = other)
+{
   "reason_type": "changed_mind",
   "reason_description": "Customer pressed C on WhatsApp"
 }
@@ -1617,8 +1976,16 @@
       <c r="C16" t="str">
         <v>GET https://api.metrogini.com/api/common/faq</v>
       </c>
-      <c r="D16" t="str">
-        <v>No body. Optional: none</v>
+      <c r="D16" t="str" xml:space="preserve">
+        <v xml:space="preserve">========== FIELD GUIDE ==========
+REQUIRED: none (no body)
+OPTIONAL: none
+=================================
+How to use in Postman:
+- OPTIONAL query params are unchecked (disabled). Tick only if needed.
+- Body tab sends clean JSON (no comments).
+- Annotated body below is documentation for Gallabox (which fields are optional).
+No body. Optional: none</v>
       </c>
       <c r="E16" t="str" xml:space="preserve">
         <v xml:space="preserve">{
@@ -1646,8 +2013,16 @@
       <c r="C17" t="str">
         <v>GET https://api.metrogini.com/api/common/how-we-work</v>
       </c>
-      <c r="D17" t="str">
-        <v>No body. Optional: none</v>
+      <c r="D17" t="str" xml:space="preserve">
+        <v xml:space="preserve">========== FIELD GUIDE ==========
+REQUIRED: none (no body)
+OPTIONAL: none
+=================================
+How to use in Postman:
+- OPTIONAL query params are unchecked (disabled). Tick only if needed.
+- Body tab sends clean JSON (no comments).
+- Annotated body below is documentation for Gallabox (which fields are optional).
+No body. Optional: none</v>
       </c>
       <c r="E17" t="str" xml:space="preserve">
         <v xml:space="preserve">{
@@ -1675,8 +2050,16 @@
       <c r="C18" t="str">
         <v>GET https://api.metrogini.com/api/common/know-about-us</v>
       </c>
-      <c r="D18" t="str">
-        <v>No body. Optional: none</v>
+      <c r="D18" t="str" xml:space="preserve">
+        <v xml:space="preserve">========== FIELD GUIDE ==========
+REQUIRED: none (no body)
+OPTIONAL: none
+=================================
+How to use in Postman:
+- OPTIONAL query params are unchecked (disabled). Tick only if needed.
+- Body tab sends clean JSON (no comments).
+- Annotated body below is documentation for Gallabox (which fields are optional).
+No body. Optional: none</v>
       </c>
       <c r="E18" t="str" xml:space="preserve">
         <v xml:space="preserve">{
@@ -1744,7 +2127,18 @@
         <v>GET https://api.metrogini.com/api/whatsapp/crm/inactive-app-users</v>
       </c>
       <c r="D2" t="str" xml:space="preserve">
-        <v xml:space="preserve">Query optional: hours (default 48), limit (default 100, max 500)
+        <v xml:space="preserve">========== FIELD GUIDE ==========
+REQUIRED: none (no body)
+OPTIONAL: hours (default 48), limit (default 100, max 500)
+=================================
+How to use in Postman:
+- OPTIONAL query params are unchecked (disabled). Tick only if needed.
+- Body tab sends clean JSON (no comments).
+- Annotated body below is documentation for Gallabox (which fields are optional).
+Query params:
+  • hours: REQUIRED (or usually sent) — Optional. Default 48
+  • limit: OPTIONAL — Optional. Default 100
+Query optional: hours (default 48), limit (default 100, max 500)
 Users with 0 completed orders and created_at older than hours.</v>
       </c>
       <c r="E2" t="str" xml:space="preserve">
@@ -1774,7 +2168,19 @@
         <v>POST https://api.metrogini.com/api/whatsapp/session</v>
       </c>
       <c r="D3" t="str" xml:space="preserve">
-        <v xml:space="preserve">{
+        <v xml:space="preserve">========== FIELD GUIDE ==========
+REQUIRED: mobile
+OPTIONAL: none
+=================================
+How to use in Postman:
+- OPTIONAL query params are unchecked (disabled). Tick only if needed.
+- Body tab sends clean JSON (no comments).
+- Annotated body below is documentation for Gallabox (which fields are optional).
+Annotated body (docs only — do not paste comments into Body):
+{
+  "mobile": "{{mobile}}"  // REQUIRED
+}
+{
   "mobile": "9004186460"
 }
 Required: mobile
@@ -1814,8 +2220,16 @@
       <c r="C4" t="str">
         <v>GET https://api.metrogini.com/api/user/profile</v>
       </c>
-      <c r="D4" t="str">
-        <v>No body. Optional: none</v>
+      <c r="D4" t="str" xml:space="preserve">
+        <v xml:space="preserve">========== FIELD GUIDE ==========
+REQUIRED: none (no body)
+OPTIONAL: none
+=================================
+How to use in Postman:
+- OPTIONAL query params are unchecked (disabled). Tick only if needed.
+- Body tab sends clean JSON (no comments).
+- Annotated body below is documentation for Gallabox (which fields are optional).
+No body. Optional: none</v>
       </c>
       <c r="E4" t="str" xml:space="preserve">
         <v xml:space="preserve">{
@@ -1881,7 +2295,19 @@
         <v>POST https://api.metrogini.com/api/whatsapp/session</v>
       </c>
       <c r="D2" t="str" xml:space="preserve">
-        <v xml:space="preserve">{
+        <v xml:space="preserve">========== FIELD GUIDE ==========
+REQUIRED: mobile
+OPTIONAL: none
+=================================
+How to use in Postman:
+- OPTIONAL query params are unchecked (disabled). Tick only if needed.
+- Body tab sends clean JSON (no comments).
+- Annotated body below is documentation for Gallabox (which fields are optional).
+Annotated body (docs only — do not paste comments into Body):
+{
+  "mobile": "{{mobile}}"  // REQUIRED
+}
+{
   "mobile": "9004186460"
 }
 Required: mobile
@@ -1923,7 +2349,19 @@
         <v>POST https://api.metrogini.com/api/whatsapp/customer/lookup</v>
       </c>
       <c r="D3" t="str" xml:space="preserve">
-        <v xml:space="preserve">{
+        <v xml:space="preserve">========== FIELD GUIDE ==========
+REQUIRED: mobile
+OPTIONAL: none
+=================================
+How to use in Postman:
+- OPTIONAL query params are unchecked (disabled). Tick only if needed.
+- Body tab sends clean JSON (no comments).
+- Annotated body below is documentation for Gallabox (which fields are optional).
+Annotated body (docs only — do not paste comments into Body):
+{
+  "mobile": "{{mobile}}"  // REQUIRED
+}
+{
   "mobile": "9004186460"
 }
 Required: mobile
@@ -1965,7 +2403,15 @@
         <v>GET https://api.metrogini.com/api/user/address</v>
       </c>
       <c r="D4" t="str" xml:space="preserve">
-        <v xml:space="preserve">No body. Optional: none
+        <v xml:space="preserve">========== FIELD GUIDE ==========
+REQUIRED: none (no body)
+OPTIONAL: none
+=================================
+How to use in Postman:
+- OPTIONAL query params are unchecked (disabled). Tick only if needed.
+- Body tab sends clean JSON (no comments).
+- Annotated body below is documentation for Gallabox (which fields are optional).
+No body. Optional: none
 Book = Scenario 1 garment → pickup → confirm. Registered user usually has an address.</v>
       </c>
       <c r="E4" t="str" xml:space="preserve">
@@ -1996,8 +2442,16 @@
       <c r="C5" t="str">
         <v>GET https://api.metrogini.com/api/common/faq</v>
       </c>
-      <c r="D5" t="str">
-        <v>No body. Optional: none. Same Know more as Scenario 1.</v>
+      <c r="D5" t="str" xml:space="preserve">
+        <v xml:space="preserve">========== FIELD GUIDE ==========
+REQUIRED: none (no body)
+OPTIONAL: none. Same Know more as Scenario 1.
+=================================
+How to use in Postman:
+- OPTIONAL query params are unchecked (disabled). Tick only if needed.
+- Body tab sends clean JSON (no comments).
+- Annotated body below is documentation for Gallabox (which fields are optional).
+No body. Optional: none. Same Know more as Scenario 1.</v>
       </c>
       <c r="E5" t="str" xml:space="preserve">
         <v xml:space="preserve">{
@@ -2025,8 +2479,16 @@
       <c r="C6" t="str">
         <v>GET https://api.metrogini.com/api/common/how-we-work</v>
       </c>
-      <c r="D6" t="str">
-        <v>No body. Optional: none</v>
+      <c r="D6" t="str" xml:space="preserve">
+        <v xml:space="preserve">========== FIELD GUIDE ==========
+REQUIRED: none (no body)
+OPTIONAL: none
+=================================
+How to use in Postman:
+- OPTIONAL query params are unchecked (disabled). Tick only if needed.
+- Body tab sends clean JSON (no comments).
+- Annotated body below is documentation for Gallabox (which fields are optional).
+No body. Optional: none</v>
       </c>
       <c r="E6" t="str" xml:space="preserve">
         <v xml:space="preserve">{
@@ -2054,8 +2516,16 @@
       <c r="C7" t="str">
         <v>GET https://api.metrogini.com/api/common/know-about-us</v>
       </c>
-      <c r="D7" t="str">
-        <v>No body. Optional: none</v>
+      <c r="D7" t="str" xml:space="preserve">
+        <v xml:space="preserve">========== FIELD GUIDE ==========
+REQUIRED: none (no body)
+OPTIONAL: none
+=================================
+How to use in Postman:
+- OPTIONAL query params are unchecked (disabled). Tick only if needed.
+- Body tab sends clean JSON (no comments).
+- Annotated body below is documentation for Gallabox (which fields are optional).
+No body. Optional: none</v>
       </c>
       <c r="E7" t="str" xml:space="preserve">
         <v xml:space="preserve">{
@@ -2082,8 +2552,20 @@
       <c r="C8" t="str">
         <v>GET https://api.metrogini.com/api/user/order/getUserOrder</v>
       </c>
-      <c r="D8" t="str">
-        <v>Query optional: status, time, page, limit</v>
+      <c r="D8" t="str" xml:space="preserve">
+        <v xml:space="preserve">========== FIELD GUIDE ==========
+REQUIRED: none (no body)
+OPTIONAL: status, time, page, limit
+=================================
+How to use in Postman:
+- OPTIONAL query params are unchecked (disabled). Tick only if needed.
+- Body tab sends clean JSON (no comments).
+- Annotated body below is documentation for Gallabox (which fields are optional).
+Query params:
+  • status: OPTIONAL — Optional filter
+  • page: OPTIONAL — Optional
+  • limit: OPTIONAL — Optional
+Query optional: status, time, page, limit</v>
       </c>
       <c r="E8" t="str" xml:space="preserve">
         <v xml:space="preserve">{
@@ -2111,7 +2593,15 @@
         <v>GET https://api.metrogini.com/api/user/order/:id/Orderdetail</v>
       </c>
       <c r="D9" t="str" xml:space="preserve">
-        <v xml:space="preserve">Path required: id
+        <v xml:space="preserve">========== FIELD GUIDE ==========
+REQUIRED: id
+OPTIONAL: none
+=================================
+How to use in Postman:
+- OPTIONAL query params are unchecked (disabled). Tick only if needed.
+- Body tab sends clean JSON (no comments).
+- Annotated body below is documentation for Gallabox (which fields are optional).
+Path required: id
 Optional: none</v>
       </c>
       <c r="E9" t="str" xml:space="preserve">
@@ -2177,7 +2667,15 @@
         <v>GET https://api.metrogini.com/api/whatsapp/customer/:mobile/abandoned-booking</v>
       </c>
       <c r="D2" t="str" xml:space="preserve">
-        <v xml:space="preserve">Path required: mobile
+        <v xml:space="preserve">========== FIELD GUIDE ==========
+REQUIRED: mobile
+OPTIONAL: none
+=================================
+How to use in Postman:
+- OPTIONAL query params are unchecked (disabled). Tick only if needed.
+- Body tab sends clean JSON (no comments).
+- Annotated body below is documentation for Gallabox (which fields are optional).
+Path required: mobile
 Optional: none</v>
       </c>
       <c r="E2" t="str" xml:space="preserve">
@@ -2206,7 +2704,19 @@
         <v>POST https://api.metrogini.com/api/whatsapp/session</v>
       </c>
       <c r="D3" t="str" xml:space="preserve">
-        <v xml:space="preserve">{
+        <v xml:space="preserve">========== FIELD GUIDE ==========
+REQUIRED: mobile
+OPTIONAL: none
+=================================
+How to use in Postman:
+- OPTIONAL query params are unchecked (disabled). Tick only if needed.
+- Body tab sends clean JSON (no comments).
+- Annotated body below is documentation for Gallabox (which fields are optional).
+Annotated body (docs only — do not paste comments into Body):
+{
+  "mobile": "{{mobile}}"  // REQUIRED
+}
+{
   "mobile": "9004186460"
 }
 Required: mobile
@@ -2247,7 +2757,15 @@
         <v>GET https://api.metrogini.com/api/user/order/:id/review</v>
       </c>
       <c r="D4" t="str" xml:space="preserve">
-        <v xml:space="preserve">Path: draft order_id from abandoned-booking
+        <v xml:space="preserve">========== FIELD GUIDE ==========
+REQUIRED: none (no body)
+OPTIONAL: none
+=================================
+How to use in Postman:
+- OPTIONAL query params are unchecked (disabled). Tick only if needed.
+- Body tab sends clean JSON (no comments).
+- Annotated body below is documentation for Gallabox (which fields are optional).
+Path: draft order_id from abandoned-booking
 Optional: none</v>
       </c>
       <c r="E4" t="str" xml:space="preserve">
@@ -2273,7 +2791,22 @@
         <v>POST https://api.metrogini.com/api/user/order/:id/complete-order</v>
       </c>
       <c r="D5" t="str" xml:space="preserve">
-        <v xml:space="preserve">{
+        <v xml:space="preserve">========== FIELD GUIDE ==========
+REQUIRED: service_type_id, pickup_date, pickup_slot_id, next_delivery_date
+OPTIONAL: none
+=================================
+How to use in Postman:
+- OPTIONAL query params are unchecked (disabled). Tick only if needed.
+- Body tab sends clean JSON (no comments).
+- Annotated body below is documentation for Gallabox (which fields are optional).
+Annotated body (docs only — do not paste comments into Body):
+{
+  "service_type_id": 1,  // REQUIRED
+  "pickup_date": "2026-09-10",  // REQUIRED
+  "pickup_slot_id": 1,  // REQUIRED
+  "next_delivery_date": "2026-09-13"  // REQUIRED
+}
+{
   "service_type_id": 1,
   "pickup_date": "2026-09-10",
   "pickup_slot_id": 1,
@@ -2302,7 +2835,21 @@
         <v>POST https://api.metrogini.com/api/user/order/payment/:id/pay</v>
       </c>
       <c r="D6" t="str" xml:space="preserve">
-        <v xml:space="preserve">{
+        <v xml:space="preserve">========== FIELD GUIDE ==========
+REQUIRED: group_code, shift_id, day_of_week
+OPTIONAL: none
+=================================
+How to use in Postman:
+- OPTIONAL query params are unchecked (disabled). Tick only if needed.
+- Body tab sends clean JSON (no comments).
+- Annotated body below is documentation for Gallabox (which fields are optional).
+Annotated body (docs only — do not paste comments into Body):
+{
+  "group_code": "{{groupCode}}",  // REQUIRED
+  "shift_id": 1,  // REQUIRED
+  "day_of_week": 3  // REQUIRED
+}
+{
   "group_code": "MUM_WEST",
   "shift_id": 1,
   "day_of_week": 3
@@ -2372,8 +2919,20 @@
       <c r="C2" t="str">
         <v>GET https://api.metrogini.com/api/whatsapp/crm/winback</v>
       </c>
-      <c r="D2" t="str">
-        <v>Query optional: days (default 30), total_orders (default 1), limit (default 100)</v>
+      <c r="D2" t="str" xml:space="preserve">
+        <v xml:space="preserve">========== FIELD GUIDE ==========
+REQUIRED: none (no body)
+OPTIONAL: days (default 30), total_orders (default 1), limit (default 100)
+=================================
+How to use in Postman:
+- OPTIONAL query params are unchecked (disabled). Tick only if needed.
+- Body tab sends clean JSON (no comments).
+- Annotated body below is documentation for Gallabox (which fields are optional).
+Query params:
+  • days: REQUIRED (or usually sent) — Optional. Default 30
+  • total_orders: REQUIRED (or usually sent) — Optional. Default 1
+  • limit: OPTIONAL — Optional
+Query optional: days (default 30), total_orders (default 1), limit (default 100)</v>
       </c>
       <c r="E2" t="str" xml:space="preserve">
         <v xml:space="preserve">{
@@ -2406,7 +2965,19 @@
         <v>POST https://api.metrogini.com/api/whatsapp/session</v>
       </c>
       <c r="D3" t="str" xml:space="preserve">
-        <v xml:space="preserve">{
+        <v xml:space="preserve">========== FIELD GUIDE ==========
+REQUIRED: mobile
+OPTIONAL: none
+=================================
+How to use in Postman:
+- OPTIONAL query params are unchecked (disabled). Tick only if needed.
+- Body tab sends clean JSON (no comments).
+- Annotated body below is documentation for Gallabox (which fields are optional).
+Annotated body (docs only — do not paste comments into Body):
+{
+  "mobile": "{{mobile}}"  // REQUIRED
+}
+{
   "mobile": "9004186460"
 }
 Required: mobile
@@ -2446,8 +3017,16 @@
       <c r="C4" t="str">
         <v>GET https://api.metrogini.com/api/user/address</v>
       </c>
-      <c r="D4" t="str">
-        <v>No body. Optional: none</v>
+      <c r="D4" t="str" xml:space="preserve">
+        <v xml:space="preserve">========== FIELD GUIDE ==========
+REQUIRED: none (no body)
+OPTIONAL: none
+=================================
+How to use in Postman:
+- OPTIONAL query params are unchecked (disabled). Tick only if needed.
+- Body tab sends clean JSON (no comments).
+- Annotated body below is documentation for Gallabox (which fields are optional).
+No body. Optional: none</v>
       </c>
       <c r="E4" t="str" xml:space="preserve">
         <v xml:space="preserve">{
@@ -2478,7 +3057,20 @@
         <v>POST https://api.metrogini.com/api/user/order/:id/applyCoupon</v>
       </c>
       <c r="D5" t="str" xml:space="preserve">
-        <v xml:space="preserve">{
+        <v xml:space="preserve">========== FIELD GUIDE ==========
+REQUIRED: see body keys below
+OPTIONAL: coupon_code. Empty body {} reapplies loyalty coupon.
+=================================
+How to use in Postman:
+- OPTIONAL query params are unchecked (disabled). Tick only if needed.
+- Body tab sends clean JSON (no comments).
+- Annotated body below is documentation for Gallabox (which fields are optional).
+Annotated body (docs only — do not paste comments into Body):
+{
+  "coupon_code": "VALUED10"  // OPTIONAL — can omit
+}
+OPTIONAL: coupon_code. Empty body {} reapplies loyalty coupon.
+{
   "coupon_code": "VALUED10"
 }
 Optional: coupon_code — omit or {} to reapply loyalty
@@ -2543,7 +3135,20 @@
         <v>POST https://api.metrogini.com/api/whatsapp/events/emit</v>
       </c>
       <c r="D2" t="str" xml:space="preserve">
-        <v xml:space="preserve">{
+        <v xml:space="preserve">========== FIELD GUIDE ==========
+REQUIRED: event
+OPTIONAL: order_id, mobile, data
+=================================
+How to use in Postman:
+- OPTIONAL query params are unchecked (disabled). Tick only if needed.
+- Body tab sends clean JSON (no comments).
+- Annotated body below is documentation for Gallabox (which fields are optional).
+Annotated body (docs only — do not paste comments into Body):
+{
+  "event": "pickup_day_reminder",  // REQUIRED
+  "order_id": "{{orderId}}"  // OPTIONAL — can omit
+}
+{
   "event": "pickup_day_reminder",
   "order_id": 74
 }
@@ -2570,7 +3175,20 @@
         <v>POST https://api.metrogini.com/api/whatsapp/events/emit</v>
       </c>
       <c r="D3" t="str" xml:space="preserve">
-        <v xml:space="preserve">{
+        <v xml:space="preserve">========== FIELD GUIDE ==========
+REQUIRED: event
+OPTIONAL: order_id, data
+=================================
+How to use in Postman:
+- OPTIONAL query params are unchecked (disabled). Tick only if needed.
+- Body tab sends clean JSON (no comments).
+- Annotated body below is documentation for Gallabox (which fields are optional).
+Annotated body (docs only — do not paste comments into Body):
+{
+  "event": "rider_assigned",  // REQUIRED
+  "order_id": "{{orderId}}"  // OPTIONAL — can omit
+}
+{
   "event": "rider_assigned",
   "order_id": 74
 }
@@ -2597,7 +3215,15 @@
         <v>GET https://api.metrogini.com/api/user/order/:id/Orderdetail</v>
       </c>
       <c r="D4" t="str" xml:space="preserve">
-        <v xml:space="preserve">No body. Path required: id
+        <v xml:space="preserve">========== FIELD GUIDE ==========
+REQUIRED: id
+OPTIONAL: none
+=================================
+How to use in Postman:
+- OPTIONAL query params are unchecked (disabled). Tick only if needed.
+- Body tab sends clean JSON (no comments).
+- Annotated body below is documentation for Gallabox (which fields are optional).
+No body. Path required: id
 Optional: none</v>
       </c>
       <c r="E4" t="str" xml:space="preserve">
@@ -2624,7 +3250,15 @@
         <v>GET https://api.metrogini.com/api/whatsapp/orders/:id/rider</v>
       </c>
       <c r="D5" t="str" xml:space="preserve">
-        <v xml:space="preserve">Path required: id
+        <v xml:space="preserve">========== FIELD GUIDE ==========
+REQUIRED: id
+OPTIONAL: none
+=================================
+How to use in Postman:
+- OPTIONAL query params are unchecked (disabled). Tick only if needed.
+- Body tab sends clean JSON (no comments).
+- Annotated body below is documentation for Gallabox (which fields are optional).
+Path required: id
 Optional: none</v>
       </c>
       <c r="E5" t="str" xml:space="preserve">
@@ -2652,7 +3286,20 @@
         <v>PUT https://api.metrogini.com/api/user/order/:id/rescheduleOrderPickup</v>
       </c>
       <c r="D6" t="str" xml:space="preserve">
-        <v xml:space="preserve">{
+        <v xml:space="preserve">========== FIELD GUIDE ==========
+REQUIRED: pickup_date, pickup_slot_id
+OPTIONAL: none
+=================================
+How to use in Postman:
+- OPTIONAL query params are unchecked (disabled). Tick only if needed.
+- Body tab sends clean JSON (no comments).
+- Annotated body below is documentation for Gallabox (which fields are optional).
+Annotated body (docs only — do not paste comments into Body):
+{
+  "pickup_date": "2026-09-11",  // REQUIRED
+  "pickup_slot_id": 1  // REQUIRED
+}
+{
   "pickup_date": "2026-09-11",
   "pickup_slot_id": 1
 }
@@ -2679,7 +3326,19 @@
         <v>POST https://api.metrogini.com/api/user/order/:id/cancelService</v>
       </c>
       <c r="D7" t="str" xml:space="preserve">
-        <v xml:space="preserve">{
+        <v xml:space="preserve">========== FIELD GUIDE ==========
+REQUIRED: reason_type
+OPTIONAL: reason_description
+=================================
+How to use in Postman:
+- OPTIONAL query params are unchecked (disabled). Tick only if needed.
+- Body tab sends clean JSON (no comments).
+- Annotated body below is documentation for Gallabox (which fields are optional).
+Annotated body (docs only — do not paste comments into Body):
+{
+  "reason_type": "pickup_schedule_issue"  // REQUIRED
+}
+{
   "reason_type": "pickup_schedule_issue"
 }
 Required: reason_type
@@ -2744,7 +3403,20 @@
         <v>POST https://api.metrogini.com/api/whatsapp/events/emit</v>
       </c>
       <c r="D2" t="str" xml:space="preserve">
-        <v xml:space="preserve">{
+        <v xml:space="preserve">========== FIELD GUIDE ==========
+REQUIRED: event
+OPTIONAL: order_id
+=================================
+How to use in Postman:
+- OPTIONAL query params are unchecked (disabled). Tick only if needed.
+- Body tab sends clean JSON (no comments).
+- Annotated body below is documentation for Gallabox (which fields are optional).
+Annotated body (docs only — do not paste comments into Body):
+{
+  "event": "pickup_completed",  // REQUIRED
+  "order_id": "{{orderId}}"  // OPTIONAL — can omit
+}
+{
   "event": "pickup_completed",
   "order_id": 74
 }
@@ -2770,8 +3442,16 @@
       <c r="C3" t="str">
         <v>GET https://api.metrogini.com/api/user/order/:id/Orderdetail</v>
       </c>
-      <c r="D3" t="str">
-        <v>No body. Optional: none. Expect status picked_up / in_process</v>
+      <c r="D3" t="str" xml:space="preserve">
+        <v xml:space="preserve">========== FIELD GUIDE ==========
+REQUIRED: none (no body)
+OPTIONAL: none. Expect status picked_up / in_process
+=================================
+How to use in Postman:
+- OPTIONAL query params are unchecked (disabled). Tick only if needed.
+- Body tab sends clean JSON (no comments).
+- Annotated body below is documentation for Gallabox (which fields are optional).
+No body. Optional: none. Expect status picked_up / in_process</v>
       </c>
       <c r="E3" t="str" xml:space="preserve">
         <v xml:space="preserve">{
@@ -2836,7 +3516,15 @@
         <v>POST https://api.metrogini.com/api/vendor/order/:order_id/confirm-weight</v>
       </c>
       <c r="D2" t="str" xml:space="preserve">
-        <v xml:space="preserve">form-data Required: actual_weight
+        <v xml:space="preserve">========== FIELD GUIDE ==========
+REQUIRED: actual_weight
+OPTIONAL: is_stained, vendor_request_amount, stain images
+=================================
+How to use in Postman:
+- OPTIONAL query params are unchecked (disabled). Tick only if needed.
+- Body tab sends clean JSON (no comments).
+- Annotated body below is documentation for Gallabox (which fields are optional).
+form-data Required: actual_weight
 Optional: is_stained, vendor_request_amount, stain images</v>
       </c>
       <c r="E2" t="str" xml:space="preserve">
@@ -2862,8 +3550,16 @@
       <c r="C3" t="str">
         <v>POST https://api.metrogini.com/api/vendor/order/:order_id/finalize</v>
       </c>
-      <c r="D3" t="str">
-        <v>No body. Optional: none</v>
+      <c r="D3" t="str" xml:space="preserve">
+        <v xml:space="preserve">========== FIELD GUIDE ==========
+REQUIRED: none (no body)
+OPTIONAL: none
+=================================
+How to use in Postman:
+- OPTIONAL query params are unchecked (disabled). Tick only if needed.
+- Body tab sends clean JSON (no comments).
+- Annotated body below is documentation for Gallabox (which fields are optional).
+No body. Optional: none</v>
       </c>
       <c r="E3" t="str" xml:space="preserve">
         <v xml:space="preserve">{
@@ -2888,7 +3584,20 @@
         <v>POST https://api.metrogini.com/api/whatsapp/events/emit</v>
       </c>
       <c r="D4" t="str" xml:space="preserve">
-        <v xml:space="preserve">{
+        <v xml:space="preserve">========== FIELD GUIDE ==========
+REQUIRED: event
+OPTIONAL: order_id, data
+=================================
+How to use in Postman:
+- OPTIONAL query params are unchecked (disabled). Tick only if needed.
+- Body tab sends clean JSON (no comments).
+- Annotated body below is documentation for Gallabox (which fields are optional).
+Annotated body (docs only — do not paste comments into Body):
+{
+  "event": "order.weight_confirmed",  // REQUIRED
+  "order_id": "{{orderId}}"  // OPTIONAL — can omit
+}
+{
   "event": "order.weight_confirmed",
   "order_id": 74
 }
@@ -2914,8 +3623,16 @@
       <c r="C5" t="str">
         <v>GET https://api.metrogini.com/api/user/order/:id/Orderdetail</v>
       </c>
-      <c r="D5" t="str">
-        <v>No body. Optional: none</v>
+      <c r="D5" t="str" xml:space="preserve">
+        <v xml:space="preserve">========== FIELD GUIDE ==========
+REQUIRED: none (no body)
+OPTIONAL: none
+=================================
+How to use in Postman:
+- OPTIONAL query params are unchecked (disabled). Tick only if needed.
+- Body tab sends clean JSON (no comments).
+- Annotated body below is documentation for Gallabox (which fields are optional).
+No body. Optional: none</v>
       </c>
       <c r="E5" t="str" xml:space="preserve">
         <v xml:space="preserve">{
@@ -2942,7 +3659,20 @@
         <v>POST https://api.metrogini.com/api/user/order/payment/:id/create-order</v>
       </c>
       <c r="D6" t="str" xml:space="preserve">
-        <v xml:space="preserve">{
+        <v xml:space="preserve">========== FIELD GUIDE ==========
+REQUIRED: amount, payment_type
+OPTIONAL: none
+=================================
+How to use in Postman:
+- OPTIONAL query params are unchecked (disabled). Tick only if needed.
+- Body tab sends clean JSON (no comments).
+- Annotated body below is documentation for Gallabox (which fields are optional).
+Annotated body (docs only — do not paste comments into Body):
+{
+  "amount": 1185.04,  // REQUIRED
+  "payment_type": "remaining"  // REQUIRED
+}
+{
   "amount": 1185.04,
   "payment_type": "remaining"
 }
@@ -2972,7 +3702,21 @@
         <v>POST https://api.metrogini.com/api/user/order/payment/:id/verify</v>
       </c>
       <c r="D7" t="str" xml:space="preserve">
-        <v xml:space="preserve">{
+        <v xml:space="preserve">========== FIELD GUIDE ==========
+REQUIRED: razorpay_order_id, razorpay_payment_id, razorpay_signature
+OPTIONAL: none
+=================================
+How to use in Postman:
+- OPTIONAL query params are unchecked (disabled). Tick only if needed.
+- Body tab sends clean JSON (no comments).
+- Annotated body below is documentation for Gallabox (which fields are optional).
+Annotated body (docs only — do not paste comments into Body):
+{
+  "razorpay_order_id": "order_xxx",  // REQUIRED
+  "razorpay_payment_id": "pay_xxx",  // REQUIRED
+  "razorpay_signature": "sig_xxx"  // REQUIRED
+}
+{
   "razorpay_order_id": "order_xxx",
   "razorpay_payment_id": "pay_xxx",
   "razorpay_signature": "sig_xxx"
@@ -3000,8 +3744,16 @@
       <c r="C8" t="str">
         <v>POST https://api.metrogini.com/api/user/order/payment/razorpay/webhook</v>
       </c>
-      <c r="D8" t="str">
-        <v>Razorpay payment.captured payload. Optional: none (Razorpay-owned)</v>
+      <c r="D8" t="str" xml:space="preserve">
+        <v xml:space="preserve">========== FIELD GUIDE ==========
+REQUIRED: none (no body)
+OPTIONAL: none (Razorpay-owned)
+=================================
+How to use in Postman:
+- OPTIONAL query params are unchecked (disabled). Tick only if needed.
+- Body tab sends clean JSON (no comments).
+- Annotated body below is documentation for Gallabox (which fields are optional).
+Razorpay payment.captured payload. Optional: none (Razorpay-owned)</v>
       </c>
       <c r="E8" t="str" xml:space="preserve">
         <v xml:space="preserve">{

--- a/gallabox_scenarios.xlsx
+++ b/gallabox_scenarios.xlsx
@@ -408,7 +408,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F6"/>
+  <dimension ref="A1:F7"/>
   <cols>
     <col min="1" max="1" width="58.83203125" customWidth="1"/>
     <col min="2" max="2" width="42.83203125" customWidth="1"/>
@@ -497,12 +497,72 @@
         <v>SHARED APIs (used by many scenarios)</v>
       </c>
       <c r="B3" t="str">
+        <v>Add address (Gallabox simple)</v>
+      </c>
+      <c r="C3" t="str">
+        <v>POST https://api.metrogini.com/api/whatsapp/address</v>
+      </c>
+      <c r="D3" t="str" xml:space="preserve">
+        <v xml:space="preserve">========== FIELD GUIDE ==========
+REQUIRED: mobile, complete_address, pincode, name, email
+OPTIONAL: none
+=================================
+How to use in Postman:
+- OPTIONAL query params are unchecked (disabled). Tick only if needed.
+- Body tab sends clean JSON (no comments).
+- Annotated body below is documentation for Gallabox (which fields are optional).
+Annotated body (docs only — do not paste comments into Body):
+{
+  "mobile": "{{mobile}}",  // REQUIRED
+  "complete_address": "A-204, Lotus Residency, Andheri West",  // REQUIRED
+  "pincode": "{{pincode}}",  // REQUIRED
+  "name": "Karthik",  // REQUIRED
+  "email": "karthik@example.com"  // REQUIRED
+}
+Gallabox: mobile + complete_address + pincode + name + email (all required). No separate set-default call. Prefer this over POST /api/user/address.
+{
+  "mobile": "9004186460",
+  "complete_address": "A-204, Lotus Residency, Andheri West",
+  "pincode": "400058",
+  "name": "Karthik",
+  "email": "karthik@example.com"
+}
+Required: mobile, complete_address, pincode, name, email
+Optional: none
+Server splits floor/landmark from complete_address and auto-sets default. Returns access_token for booking steps.</v>
+      </c>
+      <c r="E3" t="str" xml:space="preserve">
+        <v xml:space="preserve">{
+  "success": true,
+  "message": "Address added and set as default",
+  "data": {
+    "address_id": 3,
+    "is_default": true,
+    "pincode": "400058",
+    "complete_address": "A-204, Lotus Residency, Andheri West",
+    "floor": "A-204",
+    "landmark": "Lotus Residency",
+    "name": "Karthik",
+    "email": "karthik@example.com",
+    "access_token": "eyJ..."
+  }
+}</v>
+      </c>
+      <c r="F3" t="str">
+        <v>Gallabox secret</v>
+      </c>
+    </row>
+    <row r="4" xml:space="preserve">
+      <c r="A4" t="str">
+        <v>SHARED APIs (used by many scenarios)</v>
+      </c>
+      <c r="B4" t="str">
         <v>Customer lookup by mobile</v>
       </c>
-      <c r="C3" t="str">
+      <c r="C4" t="str">
         <v>POST https://api.metrogini.com/api/whatsapp/customer/lookup</v>
       </c>
-      <c r="D3" t="str" xml:space="preserve">
+      <c r="D4" t="str" xml:space="preserve">
         <v xml:space="preserve">========== FIELD GUIDE ==========
 REQUIRED: mobile
 OPTIONAL: none
@@ -522,7 +582,7 @@
 Optional: none
 Also: GET /api/whatsapp/customer/lookup?mobile=</v>
       </c>
-      <c r="E3" t="str" xml:space="preserve">
+      <c r="E4" t="str" xml:space="preserve">
         <v xml:space="preserve">{
   "success": true,
   "message": "Customer found",
@@ -543,21 +603,21 @@
   }
 }</v>
       </c>
-      <c r="F3" t="str">
+      <c r="F4" t="str">
         <v>Gallabox secret</v>
       </c>
     </row>
-    <row r="4" xml:space="preserve">
-      <c r="A4" t="str">
+    <row r="5" xml:space="preserve">
+      <c r="A5" t="str">
         <v>SHARED APIs (used by many scenarios)</v>
       </c>
-      <c r="B4" t="str">
+      <c r="B5" t="str">
         <v>Login or register (OTP fallback)</v>
       </c>
-      <c r="C4" t="str">
+      <c r="C5" t="str">
         <v>POST https://api.metrogini.com/api/user/login-or-register</v>
       </c>
-      <c r="D4" t="str" xml:space="preserve">
+      <c r="D5" t="str" xml:space="preserve">
         <v xml:space="preserve">========== FIELD GUIDE ==========
 REQUIRED: mobile
 OPTIONAL: none
@@ -576,7 +636,7 @@
 Required: mobile
 Optional: none</v>
       </c>
-      <c r="E4" t="str" xml:space="preserve">
+      <c r="E5" t="str" xml:space="preserve">
         <v xml:space="preserve">{
   "success": true,
   "message": "OTP sent successfully",
@@ -586,21 +646,21 @@
   }
 }</v>
       </c>
-      <c r="F4" t="str">
+      <c r="F5" t="str">
         <v>No</v>
       </c>
     </row>
-    <row r="5" xml:space="preserve">
-      <c r="A5" t="str">
+    <row r="6" xml:space="preserve">
+      <c r="A6" t="str">
         <v>SHARED APIs (used by many scenarios)</v>
       </c>
-      <c r="B5" t="str">
+      <c r="B6" t="str">
         <v>Verify OTP (OTP fallback)</v>
       </c>
-      <c r="C5" t="str">
+      <c r="C6" t="str">
         <v>POST https://api.metrogini.com/api/user/verify-otp</v>
       </c>
-      <c r="D5" t="str" xml:space="preserve">
+      <c r="D6" t="str" xml:space="preserve">
         <v xml:space="preserve">========== FIELD GUIDE ==========
 REQUIRED: mobile, otp
 OPTIONAL: none
@@ -621,7 +681,7 @@
 Required: mobile, otp
 Optional: none</v>
       </c>
-      <c r="E5" t="str" xml:space="preserve">
+      <c r="E6" t="str" xml:space="preserve">
         <v xml:space="preserve">{
   "success": true,
   "data": {
@@ -631,21 +691,21 @@
   }
 }</v>
       </c>
-      <c r="F5" t="str">
+      <c r="F6" t="str">
         <v>No</v>
       </c>
     </row>
-    <row r="6" xml:space="preserve">
-      <c r="A6" t="str">
+    <row r="7" xml:space="preserve">
+      <c r="A7" t="str">
         <v>SHARED APIs (used by many scenarios)</v>
       </c>
-      <c r="B6" t="str">
+      <c r="B7" t="str">
         <v>Emit event to Gallabox (test outbound)</v>
       </c>
-      <c r="C6" t="str">
+      <c r="C7" t="str">
         <v>POST https://api.metrogini.com/api/whatsapp/events/emit</v>
       </c>
-      <c r="D6" t="str" xml:space="preserve">
+      <c r="D7" t="str" xml:space="preserve">
         <v xml:space="preserve">========== FIELD GUIDE ==========
 REQUIRED: event
 OPTIONAL: order_id, mobile, data
@@ -670,19 +730,19 @@
 Optional: order_id, mobile, data
 Events: booking_confirmed, pickup_day_reminder, rider_assigned, pickup_completed, vendor_received, weight_confirmed, order.weight_confirmed, order.finalized, payment_received, out_for_delivery, delivered, delayed, cancelled</v>
       </c>
-      <c r="E6" t="str" xml:space="preserve">
+      <c r="E7" t="str" xml:space="preserve">
         <v xml:space="preserve">{
   "success": true,
   "message": "Event queued for order"
 }</v>
       </c>
-      <c r="F6" t="str">
+      <c r="F7" t="str">
         <v>Gallabox secret</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:F6"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:F7"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -1600,7 +1660,7 @@
   "name": "Karthik",  // REQUIRED
   "email": "karthik@example.com"  // REQUIRED
 }
-Gallabox: mobile + complete_address + pincode + name + email (all required). No separate set-default call.
+Gallabox: mobile + complete_address + pincode + name + email (all required). No separate set-default call. Prefer this over POST /api/user/address.
 {
   "mobile": "9004186460",
   "complete_address": "A-204, Lotus Residency, Andheri West",
@@ -2879,7 +2939,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F5"/>
+  <dimension ref="A1:F6"/>
   <cols>
     <col min="1" max="1" width="58.83203125" customWidth="1"/>
     <col min="2" max="2" width="42.83203125" customWidth="1"/>
@@ -3026,7 +3086,8 @@
 - OPTIONAL query params are unchecked (disabled). Tick only if needed.
 - Body tab sends clean JSON (no comments).
 - Annotated body below is documentation for Gallabox (which fields are optional).
-No body. Optional: none</v>
+No body. Optional: none
+If customer picks Yes → use this address. If No → next request (WhatsApp Add address).</v>
       </c>
       <c r="E4" t="str" xml:space="preserve">
         <v xml:space="preserve">{
@@ -3051,12 +3112,72 @@
         <v>Scenario 5 — Retention: One-Time Customer, No Repeat Order</v>
       </c>
       <c r="B5" t="str">
+        <v>Change address (Gallabox simple)</v>
+      </c>
+      <c r="C5" t="str">
+        <v>POST https://api.metrogini.com/api/whatsapp/address</v>
+      </c>
+      <c r="D5" t="str" xml:space="preserve">
+        <v xml:space="preserve">========== FIELD GUIDE ==========
+REQUIRED: mobile, complete_address, pincode, name, email. Auto-sets default.
+OPTIONAL: none
+=================================
+How to use in Postman:
+- OPTIONAL query params are unchecked (disabled). Tick only if needed.
+- Body tab sends clean JSON (no comments).
+- Annotated body below is documentation for Gallabox (which fields are optional).
+Annotated body (docs only — do not paste comments into Body):
+{
+  "mobile": "{{mobile}}",  // REQUIRED
+  "complete_address": "A-204, Lotus Residency, Andheri West",  // REQUIRED
+  "pincode": "{{pincode}}",  // REQUIRED
+  "name": "Karthik",  // REQUIRED
+  "email": "karthik@example.com"  // REQUIRED
+}
+Scenario 5: customer chose No, change address. Same as Scenario 1 WhatsApp add-address. Required: mobile, complete_address, pincode, name, email. Auto-sets default.
+{
+  "mobile": "9004186460",
+  "complete_address": "A-204, Lotus Residency, Andheri West",
+  "pincode": "400058",
+  "name": "Karthik",
+  "email": "karthik@example.com"
+}
+Required: mobile, complete_address, pincode, name, email
+Optional: none
+Server splits floor/landmark from complete_address and auto-sets default. Returns access_token for booking steps.</v>
+      </c>
+      <c r="E5" t="str" xml:space="preserve">
+        <v xml:space="preserve">{
+  "success": true,
+  "message": "Address added and set as default",
+  "data": {
+    "address_id": 3,
+    "is_default": true,
+    "pincode": "400058",
+    "complete_address": "A-204, Lotus Residency, Andheri West",
+    "floor": "A-204",
+    "landmark": "Lotus Residency",
+    "name": "Karthik",
+    "email": "karthik@example.com",
+    "access_token": "eyJ..."
+  }
+}</v>
+      </c>
+      <c r="F5" t="str">
+        <v>Gallabox secret</v>
+      </c>
+    </row>
+    <row r="6" xml:space="preserve">
+      <c r="A6" t="str">
+        <v>Scenario 5 — Retention: One-Time Customer, No Repeat Order</v>
+      </c>
+      <c r="B6" t="str">
         <v>Apply coupon (VALUED10 / win-back)</v>
       </c>
-      <c r="C5" t="str">
+      <c r="C6" t="str">
         <v>POST https://api.metrogini.com/api/user/order/:id/applyCoupon</v>
       </c>
-      <c r="D5" t="str" xml:space="preserve">
+      <c r="D6" t="str" xml:space="preserve">
         <v xml:space="preserve">========== FIELD GUIDE ==========
 REQUIRED: see body keys below
 OPTIONAL: coupon_code. Empty body {} reapplies loyalty coupon.
@@ -3076,18 +3197,18 @@
 Optional: coupon_code — omit or {} to reapply loyalty
 Txt also listed POST /api/whatsapp/offers/apply — not built; use this.</v>
       </c>
-      <c r="E5" t="str" xml:space="preserve">
+      <c r="E6" t="str" xml:space="preserve">
         <v xml:space="preserve">{
   "message": "Coupon applied successfully"
 }</v>
       </c>
-      <c r="F5" t="str">
+      <c r="F6" t="str">
         <v>Yes (user Bearer)</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:F5"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:F6"/>
   </ignoredErrors>
 </worksheet>
 </file>
